--- a/data/trans_camb/P1432-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1432-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,0</t>
+          <t>-3,08; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,57</t>
+          <t>-1,82; 1,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,98</t>
+          <t>-3,26; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,27</t>
+          <t>-2,52; 2,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,08</t>
+          <t>-2,39; 0,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,34</t>
+          <t>-1,67; 1,36</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 233,47</t>
+          <t>-100,0; 260,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 315,6</t>
+          <t>-82,81; 370,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,8</t>
+          <t>-100,0; 53,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 237,92</t>
+          <t>-74,02; 207,98</t>
         </is>
       </c>
     </row>
@@ -787,27 +787,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,43</t>
+          <t>-1,03; 0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,87</t>
+          <t>-0,73; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,87</t>
+          <t>-0,79; 3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,77</t>
+          <t>-2,12; 0,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,38</t>
+          <t>-0,6; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 403,95</t>
+          <t>-43,25; 352,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 195,28</t>
+          <t>-86,98; 105,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 250,66</t>
+          <t>-46,81; 231,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 115,39</t>
+          <t>-76,54; 100,94</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; -0,3</t>
+          <t>-3,0; -0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; -0,3</t>
+          <t>-2,99; -0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,31</t>
+          <t>-3,0; 0,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -0,57</t>
+          <t>-3,68; -0,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,28</t>
+          <t>-2,18; -0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,74</t>
+          <t>-2,61; -0,67</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,6</t>
+          <t>-100,0; 123,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,79</t>
+          <t>-100,0; 31,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,94</t>
+          <t>-1,18; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,33</t>
+          <t>-1,68; 0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,62</t>
+          <t>-0,34; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,81</t>
+          <t>1,45; 6,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,43</t>
+          <t>-0,43; 1,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,95</t>
+          <t>0,41; 3,0</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-97,72; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,28; —</t>
+          <t>47,48; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 696,41</t>
+          <t>-57,0; 623,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,07; 1109,09</t>
+          <t>17,21; 1108,63</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,6</t>
+          <t>0,49; 6,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,46</t>
+          <t>0,93; 7,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,0</t>
+          <t>-3,51; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,74</t>
+          <t>1,2; 5,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,43</t>
+          <t>-1,3; 0,22</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,54; —</t>
+          <t>-27,44; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,95; —</t>
+          <t>50,83; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,72</t>
+          <t>-1,09; 0,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,27</t>
+          <t>-0,05; 3,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,31</t>
+          <t>-0,62; 3,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,41</t>
+          <t>-1,27; 2,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,82</t>
+          <t>-0,5; 1,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,17</t>
+          <t>-0,28; 2,17</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 997,62</t>
+          <t>-62,16; 930,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 1117,01</t>
+          <t>-46,59; 961,16</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,11</t>
+          <t>-0,52; 2,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,44</t>
+          <t>-1,52; 0,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,74</t>
+          <t>-0,52; 1,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,34</t>
+          <t>0,46; 3,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,53</t>
+          <t>-0,13; 1,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,64</t>
+          <t>-0,02; 1,65</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 567,59</t>
+          <t>-51,39; 537,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,39</t>
+          <t>-100,0; 173,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 897,57</t>
+          <t>-63,36; 607,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,49; 1739,97</t>
+          <t>-11,53; 1135,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 387,03</t>
+          <t>-21,83; 400,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 369,61</t>
+          <t>-8,8; 395,82</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -1,05</t>
+          <t>-3,46; -1,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -1,12</t>
+          <t>-3,58; -1,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,16</t>
+          <t>-3,23; -0,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,79</t>
+          <t>-3,57; -0,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -1,01</t>
+          <t>-2,91; -0,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,09; -1,26</t>
+          <t>-3,13; -1,27</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-96,69; -44,65</t>
+          <t>-100,0; -48,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -43,48</t>
+          <t>-100,0; -45,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-82,12; -3,93</t>
+          <t>-82,72; -1,17</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-91,79; -31,56</t>
+          <t>-93,46; -34,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -44,84</t>
+          <t>-85,65; -43,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-92,2; -57,03</t>
+          <t>-92,29; -56,55</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,02</t>
+          <t>-0,88; 0,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,03; -0,14</t>
+          <t>-1,03; -0,18</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,78</t>
+          <t>-0,48; 0,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,58</t>
+          <t>-0,67; 0,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,2</t>
+          <t>-0,56; 0,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,07</t>
+          <t>-0,63; 0,07</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 2,06</t>
+          <t>-65,09; 11,48</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-74,3; -17,1</t>
+          <t>-75,09; -19,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 66,75</t>
+          <t>-27,75; 62,11</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 50,63</t>
+          <t>-37,37; 44,79</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 18,4</t>
+          <t>-37,29; 18,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 8,09</t>
+          <t>-43,77; 6,21</t>
         </is>
       </c>
     </row>
